--- a/docs/assets/infraestructura/s2-e1-declaracion-aplicabilidad.xlsx
+++ b/docs/assets/infraestructura/s2-e1-declaracion-aplicabilidad.xlsx
@@ -876,7 +876,7 @@
         <v>Parcial</v>
       </c>
       <c r="G16" t="str">
-        <v>Reglas por rol probadas 19/19 y sin publicar; roles MySQL; UFW</v>
+        <v>Reglas por rol probadas 19/19 y publicadas el 2026-10-24; roles MySQL; UFW</v>
       </c>
     </row>
     <row r="17">
@@ -1957,7 +1957,7 @@
         <v>Parcial</v>
       </c>
       <c r="G63" t="str">
-        <v>Reglas corregidas sin publicar; vistas MySQL para reportes</v>
+        <v>Reglas corregidas publicadas el 2026-10-24; vistas MySQL para reportes</v>
       </c>
     </row>
     <row r="64">
@@ -2187,7 +2187,7 @@
         <v>Parcial</v>
       </c>
       <c r="G73" t="str">
-        <v>MySQL: backup.js y restore.js probados; VPS, Firestore y VM pendientes</v>
+        <v>MySQL: backup.js y restore.js probados, también sobre la base real (REC-05); falta programarlos. VPS, Firestore y VM pendientes</v>
       </c>
     </row>
     <row r="74">
@@ -2833,7 +2833,7 @@
     <col min="6" max="6" width="60.83203125" customWidth="1"/>
     <col min="7" max="7" width="60.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="39.83203125" customWidth="1"/>
+    <col min="9" max="9" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2882,7 +2882,7 @@
         <v>POL-02, PRO-02</v>
       </c>
       <c r="F2" t="str">
-        <v>tests/firestore-rules/reglas.test.ts: 19/19 con las reglas corregidas; 10 fallan con las publicadas</v>
+        <v>tests/firestore-rules/reglas.test.ts: 19/19 con las reglas corregidas; 10 fallaban con las de junio. Producción: listar matrículas pagadas sin sesión → 403 (2026-10-24)</v>
       </c>
       <c r="G2" t="str">
         <v>Suite de reglas contra el ruleset publicado (KPI-01 = 0)</v>
@@ -2891,7 +2891,7 @@
         <v>4 (Bajo)</v>
       </c>
       <c r="I2" t="str">
-        <v>Pendiente (corregido en código)</v>
+        <v>Tratado (2026-10-24): publicadas desde la consola; listar matrículas pagadas sin sesión → 403</v>
       </c>
     </row>
     <row r="3">
@@ -2911,7 +2911,7 @@
         <v>POL-02</v>
       </c>
       <c r="F3" t="str">
-        <v>Grupo de 8 pruebas de roles en la suite de reglas</v>
+        <v>Grupo de 8 pruebas de roles en la suite de reglas; reglas publicadas el 2026-10-24</v>
       </c>
       <c r="G3" t="str">
         <v>Revisión de perfiles y KPI-01</v>
@@ -2920,7 +2920,7 @@
         <v>4 (Bajo)</v>
       </c>
       <c r="I3" t="str">
-        <v>Pendiente (corregido en código)</v>
+        <v>Tratado (2026-10-24): reglas publicadas; falta revisar los 4 perfiles existentes</v>
       </c>
     </row>
     <row r="4">
@@ -2940,7 +2940,7 @@
         <v>PRO-02</v>
       </c>
       <c r="F4" t="str">
-        <v>Grupo de 6 pruebas de matrícula pública con el código real de la app</v>
+        <v>Grupo de 6 pruebas de matrícula pública con el código real de la app; pre-matrícula de prueba exitosa en producción (2026-10-24)</v>
       </c>
       <c r="G4" t="str">
         <v>Matrícula de prueba sin sesión en producción</v>
@@ -2949,7 +2949,7 @@
         <v>3 (Bajo)</v>
       </c>
       <c r="I4" t="str">
-        <v>Pendiente (corregido en código)</v>
+        <v>Tratado (2026-10-24): pre-matrícula de prueba sin sesión exitosa en producción</v>
       </c>
     </row>
     <row r="5">
@@ -2978,7 +2978,7 @@
         <v>4 (Bajo)</v>
       </c>
       <c r="I5" t="str">
-        <v>En curso (CI definido en código)</v>
+        <v>En curso: reglas publicadas desde la consola el 2026-10-24; falta el secreto del CI y la comparación mensual</v>
       </c>
     </row>
     <row r="6">
@@ -2998,7 +2998,7 @@
         <v>POL-02, PRO-01</v>
       </c>
       <c r="F6" t="str">
-        <v>Retiro de copias iniciado (INC-02)</v>
+        <v>Clave 283b43c3… eliminada y reemplazada por ddf50bfe… (INC-02); fuera de la lista pública de claves de Google</v>
       </c>
       <c r="G6" t="str">
         <v>Clave anterior revocada en IAM; gitleaks sin hallazgos (KPI-04)</v>
@@ -3007,7 +3007,7 @@
         <v>5 (Medio)</v>
       </c>
       <c r="I6" t="str">
-        <v>Pendiente (retiro de copias iniciado)</v>
+        <v>Tratado (2026-10-24): clave 283b43c3… eliminada y reemplazada por ddf50bfe…; falta el escaneo de secretos en el CI</v>
       </c>
     </row>
     <row r="7">
@@ -3027,16 +3027,16 @@
         <v>POL-02</v>
       </c>
       <c r="F7" t="str">
-        <v>server/scripts/db-crear-usuarios.js (contraseñas por variables de entorno)</v>
+        <v>server/scripts/db-crear-usuarios.js (contraseñas por variables de entorno); .env versionados sin contraseñas</v>
       </c>
       <c r="G7" t="str">
-        <v>Archivos de entorno fuera del índice (KPI-04)</v>
+        <v>Ninguna contraseña en .env versionados (KPI-04)</v>
       </c>
       <c r="H7" t="str">
         <v>3 (Bajo)</v>
       </c>
       <c r="I7" t="str">
-        <v>Pendiente</v>
+        <v>Tratado con riesgo aceptado (2026-10-24): los .env no tienen contraseñas y siguen versionados por decisión del equipo; las contraseñas MySQL irán fuera de ellos</v>
       </c>
     </row>
     <row r="8">

--- a/docs/assets/infraestructura/s2-e1-declaracion-aplicabilidad.xlsx
+++ b/docs/assets/infraestructura/s2-e1-declaracion-aplicabilidad.xlsx
@@ -1106,7 +1106,7 @@
         <v>Parcial</v>
       </c>
       <c r="G26" t="str">
-        <v>Criterios de severidad (§11.2) aplicados a INC-01 a INC-05</v>
+        <v>Criterios de severidad (§11.2) aplicados a INC-01 a INC-06</v>
       </c>
     </row>
     <row r="27">
@@ -1120,7 +1120,7 @@
         <v>Sí</v>
       </c>
       <c r="D27" t="str">
-        <v>INC-01 e INC-02 abiertos</v>
+        <v>Incidentes reales registrados (INC-01 a INC-06)</v>
       </c>
       <c r="E27" t="str">
         <v>R-05</v>
@@ -1129,7 +1129,7 @@
         <v>Parcial</v>
       </c>
       <c r="G27" t="str">
-        <v>INC-01 contenido en código; publicación y rotación pendientes</v>
+        <v>INC-01, INC-02 e INC-06 contenidos y cerrados el 2026-10-24; falta el simulacro</v>
       </c>
     </row>
     <row r="28">
@@ -2023,10 +2023,10 @@
         <v>R-08</v>
       </c>
       <c r="F66" t="str">
-        <v>Planificado</v>
+        <v>Parcial</v>
       </c>
       <c r="G66" t="str">
-        <v>Presupuesto de RAM del VPS; alertas de capacidad al 80 %</v>
+        <v>Línea base medida el 2026-10-24, antes y después de alojar la capa de la academia; faltan las alertas al 80 %</v>
       </c>
     </row>
     <row r="67">
@@ -2187,7 +2187,7 @@
         <v>Parcial</v>
       </c>
       <c r="G73" t="str">
-        <v>MySQL: backup.js y restore.js probados, también sobre la base real (REC-05); falta programarlos. VPS, Firestore y VM pendientes</v>
+        <v>MySQL: respaldo diario en el VPS (temporizador de systemd desde el 2026-10-24), copia semanal verificada en la PC y restauraciones REC-05, REC-13 y REC-14. PostgreSQL del colegio, Firestore y VM pendientes</v>
       </c>
     </row>
     <row r="74">
@@ -2371,7 +2371,7 @@
         <v>Parcial</v>
       </c>
       <c r="G81" t="str">
-        <v>TLS 1.2/1.3 y HSTS en Vercel; cabeceras, CAA, SPF y DMARC pendientes</v>
+        <v>TLS 1.2/1.3 en todos los sitios; cabeceras de seguridad en la SPA y en el colegio (2026-10-24); CAA, SPF y DMARC pendientes</v>
       </c>
     </row>
     <row r="82">
@@ -2555,7 +2555,7 @@
         <v>Implementado</v>
       </c>
       <c r="G89" t="str">
-        <v>19 pruebas de reglas, 18 de API y 19 de BD; suite ejecutada contra producción en solo lectura</v>
+        <v>19 pruebas de reglas, 27 de API y 19 de BD; suite ejecutada contra producción en solo lectura</v>
       </c>
     </row>
     <row r="90">
@@ -2784,10 +2784,10 @@
         <v>5</v>
       </c>
       <c r="D5" t="str">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="str">
         <v>1</v>
@@ -2804,10 +2804,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="str">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" t="str">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="str">
         <v>1</v>
@@ -3085,16 +3085,16 @@
         <v>POL-03</v>
       </c>
       <c r="F9" t="str">
-        <v>Presupuesto de RAM (S1-E2 §10)</v>
+        <v>Presupuesto de RAM (S1-E2 §10); manual de despliegue §9.0 y §9.4</v>
       </c>
       <c r="G9" t="str">
-        <v>Línea base con free -m; alerta de MemAvailable</v>
+        <v>Línea base con free -h; alerta de MemAvailable</v>
       </c>
       <c r="H9" t="str">
         <v>6 (Medio)</v>
       </c>
       <c r="I9" t="str">
-        <v>Pendiente</v>
+        <v>Tratado en parte (2026-10-24): línea base medida; faltan la alerta y el monitoreo</v>
       </c>
     </row>
     <row r="10">
@@ -3239,7 +3239,7 @@
         <v>2 (Bajo)</v>
       </c>
       <c r="I14" t="str">
-        <v>Pendiente</v>
+        <v>Tratado (2026-10-24): 5 de 5 cabeceras y versión oculta en el Nginx del colegio; cabeceras de vercel.json en la SPA</v>
       </c>
     </row>
     <row r="15">
@@ -3636,16 +3636,16 @@
         <v>POL-04</v>
       </c>
       <c r="F28" t="str">
-        <v>server/scripts/backup.js</v>
+        <v>server/scripts/backup.js; temporizador academia-respaldo</v>
       </c>
       <c r="G28" t="str">
-        <v>REC-05; copias en 3 ubicaciones</v>
+        <v>REC-05, REC-13 y REC-14; copias en el VPS y en la PC</v>
       </c>
       <c r="H28" t="str">
         <v>3 (Bajo)</v>
       </c>
       <c r="I28" t="str">
-        <v>Pendiente</v>
+        <v>Tratado en parte (2026-10-24): respaldo diario y copia semanal verificada; falta PBS</v>
       </c>
     </row>
     <row r="29">
@@ -3674,7 +3674,7 @@
         <v>4 (Bajo)</v>
       </c>
       <c r="I29" t="str">
-        <v>Planificado</v>
+        <v>Tratado en parte (2026-10-24): servicio 24/7 en el VPS y carga inicial hecha; faltan los reintentos</v>
       </c>
     </row>
     <row r="30">
